--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2388">
   <si>
     <t>en</t>
   </si>
@@ -5773,6 +5773,18 @@
     <t>シュルカー</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift（インスパイアード）</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift（バニラ）</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -6703,6 +6715,12 @@
     <t>ウルトラキル</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>ウマムスメ</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -7001,6 +7019,12 @@
   </si>
   <si>
     <t>冬</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>ウィンター・ドロップ</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -7503,7 +7527,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16971,36 +16995,36 @@
         <v>2358</v>
       </c>
       <c r="B1183" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="B1184" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="B1185" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="B1186" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="B1187" t="s">
         <v>2366</v>
@@ -17051,19 +17075,51 @@
         <v>2377</v>
       </c>
       <c r="B1193" t="s">
-        <v>2227</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="B1194" t="s">
-        <v>2379</v>
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2387</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
